--- a/public/samples/quarterly-budget.xlsx
+++ b/public/samples/quarterly-budget.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Department</t>
   </si>
@@ -25,19 +25,85 @@
     <t xml:space="preserve">Q4</t>
   </si>
   <si>
+    <t xml:space="preserve">FY Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prior FY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YoY %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headcount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data &amp; ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Success</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">People Ops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recruiting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partnerships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procurement</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marketing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations</t>
   </si>
 </sst>
 </file>
@@ -64,105 +130,681 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2">
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="C2">
-        <v>132000</v>
+        <v>43200</v>
       </c>
       <c r="D2">
-        <v>128000</v>
+        <v>46400</v>
       </c>
       <c r="E2">
-        <v>140000</v>
+        <v>49600</v>
       </c>
       <c r="F2">
-        <v>520000</v>
+        <v>179200</v>
+      </c>
+      <c r="G2">
+        <v>170667</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>64000</v>
+        <v>46631</v>
       </c>
       <c r="C3">
-        <v>71000</v>
+        <v>49962</v>
       </c>
       <c r="D3">
-        <v>68000</v>
+        <v>53293</v>
       </c>
       <c r="E3">
-        <v>80000</v>
+        <v>56624</v>
       </c>
       <c r="F3">
-        <v>283000</v>
+        <v>206510</v>
+      </c>
+      <c r="G3">
+        <v>193906</v>
+      </c>
+      <c r="H3">
+        <v>6.5</v>
+      </c>
+      <c r="I3">
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>53262</v>
+      </c>
+      <c r="C4">
+        <v>56724</v>
+      </c>
+      <c r="D4">
+        <v>60186</v>
+      </c>
+      <c r="E4">
+        <v>63648</v>
+      </c>
+      <c r="F4">
+        <v>233820</v>
+      </c>
+      <c r="G4">
+        <v>216500</v>
+      </c>
+      <c r="H4">
         <v>8</v>
       </c>
-      <c r="B4">
-        <v>90000</v>
-      </c>
-      <c r="C4">
-        <v>95000</v>
-      </c>
-      <c r="D4">
-        <v>102000</v>
-      </c>
-      <c r="E4">
-        <v>110000</v>
-      </c>
-      <c r="F4">
-        <v>397000</v>
+      <c r="I4">
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B5">
-        <v>38000</v>
+        <v>59893</v>
       </c>
       <c r="C5">
-        <v>41000</v>
+        <v>63486</v>
       </c>
       <c r="D5">
-        <v>39000</v>
+        <v>67079</v>
       </c>
       <c r="E5">
-        <v>44000</v>
+        <v>70672</v>
       </c>
       <c r="F5">
-        <v>162000</v>
+        <v>261130</v>
+      </c>
+      <c r="G5">
+        <v>238475</v>
+      </c>
+      <c r="H5">
+        <v>9.5</v>
+      </c>
+      <c r="I5">
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>66524</v>
+      </c>
+      <c r="C6">
+        <v>70248</v>
+      </c>
+      <c r="D6">
+        <v>73972</v>
+      </c>
+      <c r="E6">
+        <v>77696</v>
+      </c>
+      <c r="F6">
+        <v>288440</v>
+      </c>
+      <c r="G6">
+        <v>259856</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>73155</v>
+      </c>
+      <c r="C7">
+        <v>77010</v>
+      </c>
+      <c r="D7">
+        <v>80865</v>
+      </c>
+      <c r="E7">
+        <v>84720</v>
+      </c>
+      <c r="F7">
+        <v>315750</v>
+      </c>
+      <c r="G7">
+        <v>280667</v>
+      </c>
+      <c r="H7">
+        <v>12.5</v>
+      </c>
+      <c r="I7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8">
+        <v>79786</v>
+      </c>
+      <c r="C8">
+        <v>83772</v>
+      </c>
+      <c r="D8">
+        <v>87758</v>
+      </c>
+      <c r="E8">
+        <v>91744</v>
+      </c>
+      <c r="F8">
+        <v>343060</v>
+      </c>
+      <c r="G8">
+        <v>326724</v>
+      </c>
+      <c r="H8">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>312000</v>
-      </c>
-      <c r="C6">
-        <v>339000</v>
-      </c>
-      <c r="D6">
-        <v>337000</v>
-      </c>
-      <c r="E6">
-        <v>374000</v>
-      </c>
-      <c r="F6">
-        <v>1362000</v>
+      <c r="I8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>86417</v>
+      </c>
+      <c r="C9">
+        <v>90534</v>
+      </c>
+      <c r="D9">
+        <v>94651</v>
+      </c>
+      <c r="E9">
+        <v>98768</v>
+      </c>
+      <c r="F9">
+        <v>370370</v>
+      </c>
+      <c r="G9">
+        <v>347765</v>
+      </c>
+      <c r="H9">
+        <v>6.5</v>
+      </c>
+      <c r="I9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10">
+        <v>93048</v>
+      </c>
+      <c r="C10">
+        <v>97296</v>
+      </c>
+      <c r="D10">
+        <v>101544</v>
+      </c>
+      <c r="E10">
+        <v>105792</v>
+      </c>
+      <c r="F10">
+        <v>397680</v>
+      </c>
+      <c r="G10">
+        <v>368222</v>
+      </c>
+      <c r="H10">
+        <v>8</v>
+      </c>
+      <c r="I10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <v>99679</v>
+      </c>
+      <c r="C11">
+        <v>104058</v>
+      </c>
+      <c r="D11">
+        <v>108437</v>
+      </c>
+      <c r="E11">
+        <v>112816</v>
+      </c>
+      <c r="F11">
+        <v>424990</v>
+      </c>
+      <c r="G11">
+        <v>388119</v>
+      </c>
+      <c r="H11">
+        <v>9.5</v>
+      </c>
+      <c r="I11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12">
+        <v>106310</v>
+      </c>
+      <c r="C12">
+        <v>110820</v>
+      </c>
+      <c r="D12">
+        <v>115330</v>
+      </c>
+      <c r="E12">
+        <v>119840</v>
+      </c>
+      <c r="F12">
+        <v>452300</v>
+      </c>
+      <c r="G12">
+        <v>407477</v>
+      </c>
+      <c r="H12">
+        <v>11</v>
+      </c>
+      <c r="I12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13">
+        <v>112941</v>
+      </c>
+      <c r="C13">
+        <v>117582</v>
+      </c>
+      <c r="D13">
+        <v>122223</v>
+      </c>
+      <c r="E13">
+        <v>126864</v>
+      </c>
+      <c r="F13">
+        <v>479610</v>
+      </c>
+      <c r="G13">
+        <v>426320</v>
+      </c>
+      <c r="H13">
+        <v>12.5</v>
+      </c>
+      <c r="I13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14">
+        <v>119572</v>
+      </c>
+      <c r="C14">
+        <v>124344</v>
+      </c>
+      <c r="D14">
+        <v>129116</v>
+      </c>
+      <c r="E14">
+        <v>133888</v>
+      </c>
+      <c r="F14">
+        <v>506920</v>
+      </c>
+      <c r="G14">
+        <v>482781</v>
+      </c>
+      <c r="H14">
+        <v>5</v>
+      </c>
+      <c r="I14">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15">
+        <v>126203</v>
+      </c>
+      <c r="C15">
+        <v>131106</v>
+      </c>
+      <c r="D15">
+        <v>136009</v>
+      </c>
+      <c r="E15">
+        <v>140912</v>
+      </c>
+      <c r="F15">
+        <v>534230</v>
+      </c>
+      <c r="G15">
+        <v>501624</v>
+      </c>
+      <c r="H15">
+        <v>6.5</v>
+      </c>
+      <c r="I15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16">
+        <v>132834</v>
+      </c>
+      <c r="C16">
+        <v>137868</v>
+      </c>
+      <c r="D16">
+        <v>142902</v>
+      </c>
+      <c r="E16">
+        <v>147936</v>
+      </c>
+      <c r="F16">
+        <v>561540</v>
+      </c>
+      <c r="G16">
+        <v>519944</v>
+      </c>
+      <c r="H16">
+        <v>8</v>
+      </c>
+      <c r="I16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17">
+        <v>139465</v>
+      </c>
+      <c r="C17">
+        <v>144630</v>
+      </c>
+      <c r="D17">
+        <v>149795</v>
+      </c>
+      <c r="E17">
+        <v>154960</v>
+      </c>
+      <c r="F17">
+        <v>588850</v>
+      </c>
+      <c r="G17">
+        <v>537763</v>
+      </c>
+      <c r="H17">
+        <v>9.5</v>
+      </c>
+      <c r="I17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18">
+        <v>146096</v>
+      </c>
+      <c r="C18">
+        <v>151392</v>
+      </c>
+      <c r="D18">
+        <v>156688</v>
+      </c>
+      <c r="E18">
+        <v>161984</v>
+      </c>
+      <c r="F18">
+        <v>616160</v>
+      </c>
+      <c r="G18">
+        <v>555099</v>
+      </c>
+      <c r="H18">
+        <v>11</v>
+      </c>
+      <c r="I18">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19">
+        <v>152727</v>
+      </c>
+      <c r="C19">
+        <v>158154</v>
+      </c>
+      <c r="D19">
+        <v>163581</v>
+      </c>
+      <c r="E19">
+        <v>169008</v>
+      </c>
+      <c r="F19">
+        <v>643470</v>
+      </c>
+      <c r="G19">
+        <v>571973</v>
+      </c>
+      <c r="H19">
+        <v>12.5</v>
+      </c>
+      <c r="I19">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20">
+        <v>159358</v>
+      </c>
+      <c r="C20">
+        <v>164916</v>
+      </c>
+      <c r="D20">
+        <v>170474</v>
+      </c>
+      <c r="E20">
+        <v>167032</v>
+      </c>
+      <c r="F20">
+        <v>661780</v>
+      </c>
+      <c r="G20">
+        <v>630267</v>
+      </c>
+      <c r="H20">
+        <v>5</v>
+      </c>
+      <c r="I20">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21">
+        <v>165989</v>
+      </c>
+      <c r="C21">
+        <v>171678</v>
+      </c>
+      <c r="D21">
+        <v>177367</v>
+      </c>
+      <c r="E21">
+        <v>174056</v>
+      </c>
+      <c r="F21">
+        <v>689090</v>
+      </c>
+      <c r="G21">
+        <v>647033</v>
+      </c>
+      <c r="H21">
+        <v>6.5</v>
+      </c>
+      <c r="I21">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22">
+        <v>172620</v>
+      </c>
+      <c r="C22">
+        <v>178440</v>
+      </c>
+      <c r="D22">
+        <v>184260</v>
+      </c>
+      <c r="E22">
+        <v>181080</v>
+      </c>
+      <c r="F22">
+        <v>716400</v>
+      </c>
+      <c r="G22">
+        <v>663333</v>
+      </c>
+      <c r="H22">
+        <v>8</v>
+      </c>
+      <c r="I22">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23">
+        <v>179251</v>
+      </c>
+      <c r="C23">
+        <v>185202</v>
+      </c>
+      <c r="D23">
+        <v>191153</v>
+      </c>
+      <c r="E23">
+        <v>188104</v>
+      </c>
+      <c r="F23">
+        <v>743710</v>
+      </c>
+      <c r="G23">
+        <v>679187</v>
+      </c>
+      <c r="H23">
+        <v>9.5</v>
+      </c>
+      <c r="I23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24">
+        <v>2411761</v>
+      </c>
+      <c r="C24">
+        <v>2512422</v>
+      </c>
+      <c r="D24">
+        <v>2613083</v>
+      </c>
+      <c r="E24">
+        <v>2677744</v>
+      </c>
+      <c r="F24">
+        <v>10215010</v>
+      </c>
+      <c r="G24">
+        <v>9413702</v>
+      </c>
+      <c r="H24">
+        <v>8.5</v>
+      </c>
+      <c r="I24">
+        <v>575</v>
       </c>
     </row>
   </sheetData>
